--- a/informes_data/Segunda FEB/2025-26/playoffs/aggregate_individual/AGG_IND_INSOLAC CAJA 87.xlsx
+++ b/informes_data/Segunda FEB/2025-26/playoffs/aggregate_individual/AGG_IND_INSOLAC CAJA 87.xlsx
@@ -562,76 +562,76 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D2" t="n">
-        <v>20.9809</v>
+        <v>19.0077</v>
       </c>
       <c r="E2" t="n">
-        <v>16.2697</v>
+        <v>14.6926</v>
       </c>
       <c r="F2" t="n">
-        <v>4.7113</v>
+        <v>4.3151</v>
       </c>
       <c r="G2" t="n">
-        <v>11.6031</v>
+        <v>10.9087</v>
       </c>
       <c r="H2" t="n">
-        <v>3.352300000000001</v>
+        <v>3.5312</v>
       </c>
       <c r="I2" t="n">
-        <v>8.2508</v>
+        <v>7.3773</v>
       </c>
       <c r="J2" t="n">
-        <v>12.2936</v>
+        <v>12.6541</v>
       </c>
       <c r="K2" t="n">
-        <v>6.337400000000001</v>
+        <v>7.9486</v>
       </c>
       <c r="L2" t="n">
-        <v>5.956300000000001</v>
+        <v>4.7056</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.6905999999999999</v>
+        <v>-1.7456</v>
       </c>
       <c r="N2" t="n">
-        <v>-2.9851</v>
+        <v>-4.4175</v>
       </c>
       <c r="O2" t="n">
-        <v>2.2944</v>
+        <v>2.6719</v>
       </c>
       <c r="P2" t="n">
-        <v>1.0241</v>
+        <v>2.2271</v>
       </c>
       <c r="Q2" t="n">
-        <v>-7.3745</v>
+        <v>-8.503</v>
       </c>
       <c r="R2" t="n">
-        <v>8.398800000000001</v>
+        <v>10.7299</v>
       </c>
       <c r="S2" t="n">
-        <v>10.0183</v>
+        <v>8.1593</v>
       </c>
       <c r="T2" t="n">
-        <v>10.8665</v>
+        <v>10.0394</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.8480000000000001</v>
+        <v>-1.8802</v>
       </c>
       <c r="V2" t="n">
-        <v>-1.6647</v>
+        <v>-2.2872</v>
       </c>
       <c r="W2" t="n">
-        <v>0.4841</v>
+        <v>0.5019</v>
       </c>
       <c r="X2" t="n">
-        <v>-2.1488</v>
+        <v>-2.7891</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A. LATORRE SANCHEZ</t>
+          <t>J. FRANCH DE PABLO</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -640,76 +640,76 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D3" t="n">
-        <v>16.3859</v>
+        <v>16.8595</v>
       </c>
       <c r="E3" t="n">
-        <v>12.0418</v>
+        <v>12.5087</v>
       </c>
       <c r="F3" t="n">
-        <v>4.343999999999999</v>
+        <v>4.3508</v>
       </c>
       <c r="G3" t="n">
-        <v>4.2353</v>
+        <v>15.4021</v>
       </c>
       <c r="H3" t="n">
-        <v>1.0943</v>
+        <v>4.4283</v>
       </c>
       <c r="I3" t="n">
-        <v>3.1409</v>
+        <v>10.9737</v>
       </c>
       <c r="J3" t="n">
-        <v>8.100300000000001</v>
+        <v>20.6243</v>
       </c>
       <c r="K3" t="n">
-        <v>4.8601</v>
+        <v>6.533</v>
       </c>
       <c r="L3" t="n">
-        <v>3.2403</v>
+        <v>14.0913</v>
       </c>
       <c r="M3" t="n">
-        <v>-3.865</v>
+        <v>-5.2222</v>
       </c>
       <c r="N3" t="n">
-        <v>-3.7657</v>
+        <v>-2.1046</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.09930000000000017</v>
+        <v>-3.1178</v>
       </c>
       <c r="P3" t="n">
-        <v>4.9163</v>
+        <v>1.2148</v>
       </c>
       <c r="Q3" t="n">
-        <v>-2.4581</v>
+        <v>-8.9079</v>
       </c>
       <c r="R3" t="n">
-        <v>7.374499999999999</v>
+        <v>10.1226</v>
       </c>
       <c r="S3" t="n">
-        <v>7.1399</v>
+        <v>-4.1482</v>
       </c>
       <c r="T3" t="n">
-        <v>4.735</v>
+        <v>-4.2194</v>
       </c>
       <c r="U3" t="n">
-        <v>2.405</v>
+        <v>0.07140000000000002</v>
       </c>
       <c r="V3" t="n">
-        <v>0.09419999999999995</v>
+        <v>4.3909</v>
       </c>
       <c r="W3" t="n">
-        <v>1.6647</v>
+        <v>5.011699999999999</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.5705</v>
+        <v>-0.6208</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>J. FRANCH DE PABLO</t>
+          <t>A. LATORRE SANCHEZ</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -718,70 +718,70 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D4" t="n">
-        <v>16.0251</v>
+        <v>13.7446</v>
       </c>
       <c r="E4" t="n">
-        <v>13.2056</v>
+        <v>10.7907</v>
       </c>
       <c r="F4" t="n">
-        <v>2.819599999999999</v>
+        <v>2.9539</v>
       </c>
       <c r="G4" t="n">
-        <v>16.3919</v>
+        <v>2.3181</v>
       </c>
       <c r="H4" t="n">
-        <v>4.2983</v>
+        <v>-0.2813999999999999</v>
       </c>
       <c r="I4" t="n">
-        <v>12.0937</v>
+        <v>2.5994</v>
       </c>
       <c r="J4" t="n">
-        <v>20.975</v>
+        <v>7.7919</v>
       </c>
       <c r="K4" t="n">
-        <v>5.666700000000001</v>
+        <v>4.492</v>
       </c>
       <c r="L4" t="n">
-        <v>15.3084</v>
+        <v>3.2996</v>
       </c>
       <c r="M4" t="n">
-        <v>-4.5831</v>
+        <v>-5.4736</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.3684</v>
+        <v>-4.7736</v>
       </c>
       <c r="O4" t="n">
-        <v>-3.2146</v>
+        <v>-0.7001000000000002</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.000100000000000211</v>
+        <v>4.6564</v>
       </c>
       <c r="Q4" t="n">
-        <v>-7.5794</v>
+        <v>-3.6442</v>
       </c>
       <c r="R4" t="n">
-        <v>7.5794</v>
+        <v>8.300599999999999</v>
       </c>
       <c r="S4" t="n">
-        <v>-3.3065</v>
+        <v>6.7024</v>
       </c>
       <c r="T4" t="n">
-        <v>-3.7321</v>
+        <v>4.9509</v>
       </c>
       <c r="U4" t="n">
-        <v>0.4255999999999998</v>
+        <v>1.7516</v>
       </c>
       <c r="V4" t="n">
-        <v>2.9395</v>
+        <v>0.06749999999999995</v>
       </c>
       <c r="W4" t="n">
-        <v>3.5418</v>
+        <v>1.6921</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.6023000000000001</v>
+        <v>-1.6246</v>
       </c>
     </row>
     <row r="5">
@@ -796,70 +796,70 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D5" t="n">
-        <v>8.1892</v>
+        <v>7.4966</v>
       </c>
       <c r="E5" t="n">
-        <v>8.992700000000001</v>
+        <v>8.054600000000001</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.8035000000000001</v>
+        <v>-0.5579000000000001</v>
       </c>
       <c r="G5" t="n">
-        <v>0.4884999999999999</v>
+        <v>-1.9076</v>
       </c>
       <c r="H5" t="n">
-        <v>1.8219</v>
+        <v>-0.1138000000000001</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.3333</v>
+        <v>-1.7937</v>
       </c>
       <c r="J5" t="n">
-        <v>5.8975</v>
+        <v>5.01</v>
       </c>
       <c r="K5" t="n">
-        <v>4.1097</v>
+        <v>3.6329</v>
       </c>
       <c r="L5" t="n">
-        <v>1.7878</v>
+        <v>1.3771</v>
       </c>
       <c r="M5" t="n">
-        <v>-5.409</v>
+        <v>-6.9175</v>
       </c>
       <c r="N5" t="n">
-        <v>-2.2876</v>
+        <v>-3.7467</v>
       </c>
       <c r="O5" t="n">
-        <v>-3.1211</v>
+        <v>-3.1708</v>
       </c>
       <c r="P5" t="n">
-        <v>2.868</v>
+        <v>5.466099999999999</v>
       </c>
       <c r="Q5" t="n">
-        <v>-4.3018</v>
+        <v>-4.2515</v>
       </c>
       <c r="R5" t="n">
-        <v>7.1696</v>
+        <v>9.7178</v>
       </c>
       <c r="S5" t="n">
-        <v>-2.5873</v>
+        <v>-2.2381</v>
       </c>
       <c r="T5" t="n">
-        <v>-1.1095</v>
+        <v>-0.5980999999999999</v>
       </c>
       <c r="U5" t="n">
-        <v>-1.4779</v>
+        <v>-1.6401</v>
       </c>
       <c r="V5" t="n">
-        <v>7.4199</v>
+        <v>6.1762</v>
       </c>
       <c r="W5" t="n">
-        <v>8.5063</v>
+        <v>7.894</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.0864</v>
+        <v>-1.7178</v>
       </c>
     </row>
     <row r="6">
@@ -874,76 +874,76 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D6" t="n">
-        <v>2.4814</v>
+        <v>0.4553999999999996</v>
       </c>
       <c r="E6" t="n">
-        <v>4.5071</v>
+        <v>2.3467</v>
       </c>
       <c r="F6" t="n">
-        <v>-2.0256</v>
+        <v>-1.8914</v>
       </c>
       <c r="G6" t="n">
-        <v>7.0304</v>
+        <v>6.4272</v>
       </c>
       <c r="H6" t="n">
-        <v>-8.4534</v>
+        <v>-9.4101</v>
       </c>
       <c r="I6" t="n">
-        <v>15.4838</v>
+        <v>15.8373</v>
       </c>
       <c r="J6" t="n">
-        <v>10.1884</v>
+        <v>10.0362</v>
       </c>
       <c r="K6" t="n">
-        <v>-4.3258</v>
+        <v>-4.478</v>
       </c>
       <c r="L6" t="n">
         <v>14.5142</v>
       </c>
       <c r="M6" t="n">
-        <v>-3.1579</v>
+        <v>-3.609</v>
       </c>
       <c r="N6" t="n">
-        <v>-4.1277</v>
+        <v>-4.932</v>
       </c>
       <c r="O6" t="n">
-        <v>0.9698000000000001</v>
+        <v>1.3232</v>
       </c>
       <c r="P6" t="n">
-        <v>1.0243</v>
+        <v>-0.8099000000000001</v>
       </c>
       <c r="Q6" t="n">
-        <v>-5.3261</v>
+        <v>-8.705400000000001</v>
       </c>
       <c r="R6" t="n">
-        <v>6.3503</v>
+        <v>7.8956</v>
       </c>
       <c r="S6" t="n">
-        <v>-2.3796</v>
+        <v>-3.2191</v>
       </c>
       <c r="T6" t="n">
-        <v>-1.5359</v>
+        <v>-1.9595</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.8438000000000001</v>
+        <v>-1.2594</v>
       </c>
       <c r="V6" t="n">
-        <v>-3.1936</v>
+        <v>-1.943</v>
       </c>
       <c r="W6" t="n">
-        <v>1.1806</v>
+        <v>2.9755</v>
       </c>
       <c r="X6" t="n">
-        <v>-4.3742</v>
+        <v>-4.9185</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A. MOODY</t>
+          <t>N. DEDOVIC</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -952,76 +952,76 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D7" t="n">
-        <v>1.1717</v>
+        <v>-0.5698999999999997</v>
       </c>
       <c r="E7" t="n">
-        <v>3.7266</v>
+        <v>-3.005999999999999</v>
       </c>
       <c r="F7" t="n">
-        <v>-2.5549</v>
+        <v>2.4361</v>
       </c>
       <c r="G7" t="n">
-        <v>-4.7554</v>
+        <v>-0.8795000000000002</v>
       </c>
       <c r="H7" t="n">
-        <v>-4.5538</v>
+        <v>-2.9981</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.2016999999999999</v>
+        <v>2.1186</v>
       </c>
       <c r="J7" t="n">
-        <v>0.7420000000000002</v>
+        <v>1.5666</v>
       </c>
       <c r="K7" t="n">
-        <v>-2.7118</v>
+        <v>0.2529000000000001</v>
       </c>
       <c r="L7" t="n">
-        <v>3.454</v>
+        <v>1.3139</v>
       </c>
       <c r="M7" t="n">
-        <v>-5.497599999999999</v>
+        <v>-2.4462</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.8419</v>
+        <v>-3.251</v>
       </c>
       <c r="O7" t="n">
-        <v>-3.6555</v>
+        <v>0.8048999999999999</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.4097999999999997</v>
+        <v>4.049</v>
       </c>
       <c r="Q7" t="n">
-        <v>-6.5551</v>
+        <v>-3.8467</v>
       </c>
       <c r="R7" t="n">
-        <v>6.1454</v>
+        <v>7.8957</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.7467</v>
+        <v>-4.2155</v>
       </c>
       <c r="T7" t="n">
-        <v>0.7913</v>
+        <v>-2.4182</v>
       </c>
       <c r="U7" t="n">
-        <v>-1.538</v>
+        <v>-1.7973</v>
       </c>
       <c r="V7" t="n">
-        <v>7.0836</v>
+        <v>0.476</v>
       </c>
       <c r="W7" t="n">
-        <v>8.7483</v>
+        <v>1.6921</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.6647</v>
+        <v>-1.216</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>W. CABRAL BUERIBERI</t>
+          <t>A. MOODY</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1030,76 +1030,76 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.1571</v>
+        <v>-0.9531999999999998</v>
       </c>
       <c r="E8" t="n">
-        <v>-3.8707</v>
+        <v>1.9305</v>
       </c>
       <c r="F8" t="n">
-        <v>2.7136</v>
+        <v>-2.8837</v>
       </c>
       <c r="G8" t="n">
-        <v>-3.4485</v>
+        <v>-6.7981</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.4308</v>
+        <v>-5.9115</v>
       </c>
       <c r="I8" t="n">
-        <v>-3.0177</v>
+        <v>-0.8863999999999999</v>
       </c>
       <c r="J8" t="n">
-        <v>0.8456999999999997</v>
+        <v>0.2602999999999999</v>
       </c>
       <c r="K8" t="n">
-        <v>1.1601</v>
+        <v>-3.1135</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.3144999999999999</v>
+        <v>3.3738</v>
       </c>
       <c r="M8" t="n">
-        <v>-4.2941</v>
+        <v>-7.058400000000001</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.5909</v>
+        <v>-2.798</v>
       </c>
       <c r="O8" t="n">
-        <v>-2.7031</v>
+        <v>-4.2605</v>
       </c>
       <c r="P8" t="n">
-        <v>-5.551115123125783e-17</v>
+        <v>-0.6072999999999998</v>
       </c>
       <c r="Q8" t="n">
-        <v>-5.5308</v>
+        <v>-8.503</v>
       </c>
       <c r="R8" t="n">
-        <v>5.5308</v>
+        <v>7.8957</v>
       </c>
       <c r="S8" t="n">
-        <v>2.0198</v>
+        <v>-1.8791</v>
       </c>
       <c r="T8" t="n">
-        <v>0.3008</v>
+        <v>0.1497000000000002</v>
       </c>
       <c r="U8" t="n">
-        <v>1.7189</v>
+        <v>-2.0287</v>
       </c>
       <c r="V8" t="n">
-        <v>0.2717999999999999</v>
+        <v>8.331399999999999</v>
       </c>
       <c r="W8" t="n">
-        <v>0.5139</v>
+        <v>10.0235</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.2421</v>
+        <v>-1.6921</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>N. DEDOVIC</t>
+          <t>L. DIBBA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1108,76 +1108,76 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.207</v>
+        <v>-2.3409</v>
       </c>
       <c r="E9" t="n">
-        <v>-4.1994</v>
+        <v>-0.6711999999999998</v>
       </c>
       <c r="F9" t="n">
-        <v>2.9924</v>
+        <v>-1.6698</v>
       </c>
       <c r="G9" t="n">
-        <v>-3.173</v>
+        <v>-0.3996</v>
       </c>
       <c r="H9" t="n">
-        <v>-3.5221</v>
+        <v>0.7332999999999996</v>
       </c>
       <c r="I9" t="n">
-        <v>0.3491000000000001</v>
+        <v>-1.1332</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.9522999999999997</v>
+        <v>3.1488</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.8435000000000001</v>
+        <v>1.8529</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.1089000000000002</v>
+        <v>1.2956</v>
       </c>
       <c r="M9" t="n">
-        <v>-2.2205</v>
+        <v>-3.5482</v>
       </c>
       <c r="N9" t="n">
-        <v>-2.6786</v>
+        <v>-1.1195</v>
       </c>
       <c r="O9" t="n">
-        <v>0.4580000000000001</v>
+        <v>-2.4287</v>
       </c>
       <c r="P9" t="n">
-        <v>4.3018</v>
+        <v>-2.0246</v>
       </c>
       <c r="Q9" t="n">
-        <v>-2.4581</v>
+        <v>-7.490899999999999</v>
       </c>
       <c r="R9" t="n">
-        <v>6.7599</v>
+        <v>5.4663</v>
       </c>
       <c r="S9" t="n">
-        <v>-3.3984</v>
+        <v>3.3096</v>
       </c>
       <c r="T9" t="n">
-        <v>-1.8633</v>
+        <v>2.918</v>
       </c>
       <c r="U9" t="n">
-        <v>-1.5351</v>
+        <v>0.3916</v>
       </c>
       <c r="V9" t="n">
-        <v>1.0626</v>
+        <v>-3.2266</v>
       </c>
       <c r="W9" t="n">
-        <v>1.0744</v>
+        <v>0.7527</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.01189999999999999</v>
+        <v>-3.9793</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>R. SANTOS JIMENEZ</t>
+          <t>W. CABRAL BUERIBERI</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1186,70 +1186,70 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.2695</v>
+        <v>-3.3564</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.3969</v>
+        <v>-7.943000000000001</v>
       </c>
       <c r="F10" t="n">
-        <v>0.1272</v>
+        <v>4.5867</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.9944</v>
+        <v>-3.5031</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.0648</v>
+        <v>-0.3404000000000005</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.9297</v>
+        <v>-3.1628</v>
       </c>
       <c r="J10" t="n">
-        <v>-2.0123</v>
+        <v>1.1382</v>
       </c>
       <c r="K10" t="n">
-        <v>-1.3155</v>
+        <v>2.0813</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.6968</v>
+        <v>-0.9430999999999999</v>
       </c>
       <c r="M10" t="n">
-        <v>0.01780000000000004</v>
+        <v>-4.6412</v>
       </c>
       <c r="N10" t="n">
-        <v>0.2507</v>
+        <v>-2.4218</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.2329</v>
+        <v>-2.2195</v>
       </c>
       <c r="P10" t="n">
-        <v>0.4096</v>
+        <v>-3.4417</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>-11.7423</v>
       </c>
       <c r="R10" t="n">
-        <v>0.4096</v>
+        <v>8.300599999999999</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.6848000000000001</v>
+        <v>3.8036</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.3846</v>
+        <v>1.4347</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.3002</v>
+        <v>2.3687</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>-0.2151999999999999</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.2259</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>-1.4411</v>
       </c>
     </row>
     <row r="11">
@@ -1264,76 +1264,76 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.9422</v>
+        <v>-4.502800000000001</v>
       </c>
       <c r="E11" t="n">
-        <v>-5.3762</v>
+        <v>-6.7526</v>
       </c>
       <c r="F11" t="n">
-        <v>2.4338</v>
+        <v>2.2499</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.4534</v>
+        <v>-1.8802</v>
       </c>
       <c r="H11" t="n">
-        <v>-7.0105</v>
+        <v>-8.339700000000001</v>
       </c>
       <c r="I11" t="n">
-        <v>5.557</v>
+        <v>6.4595</v>
       </c>
       <c r="J11" t="n">
-        <v>-1.1178</v>
+        <v>-1.0928</v>
       </c>
       <c r="K11" t="n">
-        <v>-4.7508</v>
+        <v>-5.2636</v>
       </c>
       <c r="L11" t="n">
-        <v>3.6329</v>
+        <v>4.1707</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.3355</v>
+        <v>-0.7875</v>
       </c>
       <c r="N11" t="n">
-        <v>-2.2597</v>
+        <v>-3.0762</v>
       </c>
       <c r="O11" t="n">
-        <v>1.9242</v>
+        <v>2.2888</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.6146</v>
+        <v>-0.4047999999999999</v>
       </c>
       <c r="Q11" t="n">
-        <v>-6.350300000000001</v>
+        <v>-7.2883</v>
       </c>
       <c r="R11" t="n">
-        <v>5.7357</v>
+        <v>6.8834</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.6948</v>
+        <v>-2.787</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.6919</v>
+        <v>-2.1932</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.003000000000000058</v>
+        <v>-0.5939000000000001</v>
       </c>
       <c r="V11" t="n">
-        <v>0.8205000000000002</v>
+        <v>0.5692999999999996</v>
       </c>
       <c r="W11" t="n">
-        <v>3.7839</v>
+        <v>3.8215</v>
       </c>
       <c r="X11" t="n">
-        <v>-2.9634</v>
+        <v>-3.2522</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>L. DIBBA</t>
+          <t>R. SANTOS JIMENEZ</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1342,70 +1342,70 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D12" t="n">
-        <v>-5.9032</v>
+        <v>-4.6347</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.1016</v>
+        <v>-4.8758</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.8017</v>
+        <v>0.2412</v>
       </c>
       <c r="G12" t="n">
-        <v>-2.6329</v>
+        <v>-3.6609</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.9986</v>
+        <v>-2.4505</v>
       </c>
       <c r="I12" t="n">
-        <v>-1.6343</v>
+        <v>-1.2103</v>
       </c>
       <c r="J12" t="n">
-        <v>0.5259</v>
+        <v>-3.3617</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.6345999999999998</v>
+        <v>-1.9775</v>
       </c>
       <c r="L12" t="n">
-        <v>1.1605</v>
+        <v>-1.3842</v>
       </c>
       <c r="M12" t="n">
-        <v>-3.1588</v>
+        <v>-0.2992</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.3639999999999999</v>
+        <v>-0.473</v>
       </c>
       <c r="O12" t="n">
-        <v>-2.7947</v>
+        <v>0.1739</v>
       </c>
       <c r="P12" t="n">
-        <v>-3.2775</v>
+        <v>-0.2024</v>
       </c>
       <c r="Q12" t="n">
-        <v>-7.3744</v>
+        <v>-1.0123</v>
       </c>
       <c r="R12" t="n">
-        <v>4.0969</v>
+        <v>0.8099000000000001</v>
       </c>
       <c r="S12" t="n">
-        <v>3.2009</v>
+        <v>-0.7714</v>
       </c>
       <c r="T12" t="n">
-        <v>3.021</v>
+        <v>-0.5019</v>
       </c>
       <c r="U12" t="n">
-        <v>0.1798</v>
+        <v>-0.2695</v>
       </c>
       <c r="V12" t="n">
-        <v>-3.1934</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>0.7263000000000001</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-3.9197</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -1420,70 +1420,70 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D13" t="n">
-        <v>51.7552</v>
+        <v>41.2059</v>
       </c>
       <c r="E13" t="n">
-        <v>39.79870000000001</v>
+        <v>27.07520000000001</v>
       </c>
       <c r="F13" t="n">
-        <v>11.9562</v>
+        <v>14.1309</v>
       </c>
       <c r="G13" t="n">
-        <v>22.2916</v>
+        <v>16.0271</v>
       </c>
       <c r="H13" t="n">
-        <v>-15.4672</v>
+        <v>-21.1527</v>
       </c>
       <c r="I13" t="n">
-        <v>37.7586</v>
+        <v>37.1794</v>
       </c>
       <c r="J13" t="n">
-        <v>55.486</v>
+        <v>57.77590000000001</v>
       </c>
       <c r="K13" t="n">
-        <v>7.552</v>
+        <v>11.961</v>
       </c>
       <c r="L13" t="n">
-        <v>47.93419999999999</v>
+        <v>45.8145</v>
       </c>
       <c r="M13" t="n">
-        <v>-33.1943</v>
+        <v>-41.7486</v>
       </c>
       <c r="N13" t="n">
-        <v>-23.0189</v>
+        <v>-33.1139</v>
       </c>
       <c r="O13" t="n">
-        <v>-10.1748</v>
+        <v>-8.6347</v>
       </c>
       <c r="P13" t="n">
-        <v>10.2421</v>
+        <v>10.1227</v>
       </c>
       <c r="Q13" t="n">
-        <v>-55.30860000000001</v>
+        <v>-73.89549999999998</v>
       </c>
       <c r="R13" t="n">
-        <v>65.5509</v>
+        <v>84.0181</v>
       </c>
       <c r="S13" t="n">
-        <v>7.580800000000004</v>
+        <v>2.716500000000001</v>
       </c>
       <c r="T13" t="n">
-        <v>9.397300000000001</v>
+        <v>7.602399999999998</v>
       </c>
       <c r="U13" t="n">
-        <v>-1.816700000000001</v>
+        <v>-4.885799999999999</v>
       </c>
       <c r="V13" t="n">
-        <v>11.6404</v>
+        <v>12.3393</v>
       </c>
       <c r="W13" t="n">
-        <v>30.2243</v>
+        <v>35.5909</v>
       </c>
       <c r="X13" t="n">
-        <v>-18.584</v>
+        <v>-23.2515</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/Segunda FEB/2025-26/playoffs/aggregate_individual/AGG_IND_INSOLAC CAJA 87.xlsx
+++ b/informes_data/Segunda FEB/2025-26/playoffs/aggregate_individual/AGG_IND_INSOLAC CAJA 87.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>M. JANKOVIC</t>
+          <t>J. FRANCH DE PABLO</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>6</v>
       </c>
       <c r="D2" t="n">
-        <v>19.0077</v>
+        <v>20.2137</v>
       </c>
       <c r="E2" t="n">
-        <v>14.6926</v>
+        <v>16.0471</v>
       </c>
       <c r="F2" t="n">
-        <v>4.3151</v>
+        <v>4.1666</v>
       </c>
       <c r="G2" t="n">
-        <v>10.9087</v>
+        <v>15.4021</v>
       </c>
       <c r="H2" t="n">
-        <v>3.5312</v>
+        <v>4.4283</v>
       </c>
       <c r="I2" t="n">
-        <v>7.3773</v>
+        <v>10.9737</v>
       </c>
       <c r="J2" t="n">
-        <v>12.6541</v>
+        <v>20.6243</v>
       </c>
       <c r="K2" t="n">
-        <v>7.9486</v>
+        <v>6.533</v>
       </c>
       <c r="L2" t="n">
-        <v>4.7056</v>
+        <v>14.0913</v>
       </c>
       <c r="M2" t="n">
-        <v>-1.7456</v>
+        <v>-5.2222</v>
       </c>
       <c r="N2" t="n">
-        <v>-4.4175</v>
+        <v>-2.1046</v>
       </c>
       <c r="O2" t="n">
-        <v>2.6719</v>
+        <v>-3.1178</v>
       </c>
       <c r="P2" t="n">
-        <v>2.2271</v>
+        <v>1.2148</v>
       </c>
       <c r="Q2" t="n">
-        <v>-8.503</v>
+        <v>-8.9079</v>
       </c>
       <c r="R2" t="n">
-        <v>10.7299</v>
+        <v>10.1226</v>
       </c>
       <c r="S2" t="n">
-        <v>8.1593</v>
+        <v>-0.794</v>
       </c>
       <c r="T2" t="n">
-        <v>10.0394</v>
+        <v>-0.6811</v>
       </c>
       <c r="U2" t="n">
-        <v>-1.8802</v>
+        <v>-0.1127999999999999</v>
       </c>
       <c r="V2" t="n">
-        <v>-2.2872</v>
+        <v>4.3909</v>
       </c>
       <c r="W2" t="n">
-        <v>0.5019</v>
+        <v>5.011699999999999</v>
       </c>
       <c r="X2" t="n">
-        <v>-2.7891</v>
+        <v>-0.6208</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>J. FRANCH DE PABLO</t>
+          <t>M. JANKOVIC</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,67 +643,67 @@
         <v>6</v>
       </c>
       <c r="D3" t="n">
-        <v>16.8595</v>
+        <v>13.9282</v>
       </c>
       <c r="E3" t="n">
-        <v>12.5087</v>
+        <v>8.9673</v>
       </c>
       <c r="F3" t="n">
-        <v>4.3508</v>
+        <v>4.9608</v>
       </c>
       <c r="G3" t="n">
-        <v>15.4021</v>
+        <v>10.9087</v>
       </c>
       <c r="H3" t="n">
-        <v>4.4283</v>
+        <v>3.5312</v>
       </c>
       <c r="I3" t="n">
-        <v>10.9737</v>
+        <v>7.3773</v>
       </c>
       <c r="J3" t="n">
-        <v>20.6243</v>
+        <v>12.6541</v>
       </c>
       <c r="K3" t="n">
-        <v>6.533</v>
+        <v>7.9486</v>
       </c>
       <c r="L3" t="n">
-        <v>14.0913</v>
+        <v>4.7056</v>
       </c>
       <c r="M3" t="n">
-        <v>-5.2222</v>
+        <v>-1.7456</v>
       </c>
       <c r="N3" t="n">
-        <v>-2.1046</v>
+        <v>-4.4175</v>
       </c>
       <c r="O3" t="n">
-        <v>-3.1178</v>
+        <v>2.6719</v>
       </c>
       <c r="P3" t="n">
-        <v>1.2148</v>
+        <v>2.2271</v>
       </c>
       <c r="Q3" t="n">
-        <v>-8.9079</v>
+        <v>-8.503</v>
       </c>
       <c r="R3" t="n">
-        <v>10.1226</v>
+        <v>10.7299</v>
       </c>
       <c r="S3" t="n">
-        <v>-4.1482</v>
+        <v>3.0798</v>
       </c>
       <c r="T3" t="n">
-        <v>-4.2194</v>
+        <v>4.3142</v>
       </c>
       <c r="U3" t="n">
-        <v>0.07140000000000002</v>
+        <v>-1.2343</v>
       </c>
       <c r="V3" t="n">
-        <v>4.3909</v>
+        <v>-2.2872</v>
       </c>
       <c r="W3" t="n">
-        <v>5.011699999999999</v>
+        <v>0.5019</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.6208</v>
+        <v>-2.7891</v>
       </c>
     </row>
     <row r="4">
@@ -721,13 +721,13 @@
         <v>6</v>
       </c>
       <c r="D4" t="n">
-        <v>13.7446</v>
+        <v>10.4253</v>
       </c>
       <c r="E4" t="n">
-        <v>10.7907</v>
+        <v>8.491299999999999</v>
       </c>
       <c r="F4" t="n">
-        <v>2.9539</v>
+        <v>1.934</v>
       </c>
       <c r="G4" t="n">
         <v>2.3181</v>
@@ -766,13 +766,13 @@
         <v>8.300599999999999</v>
       </c>
       <c r="S4" t="n">
-        <v>6.7024</v>
+        <v>3.3832</v>
       </c>
       <c r="T4" t="n">
-        <v>4.9509</v>
+        <v>2.6515</v>
       </c>
       <c r="U4" t="n">
-        <v>1.7516</v>
+        <v>0.7318</v>
       </c>
       <c r="V4" t="n">
         <v>0.06749999999999995</v>
@@ -799,13 +799,13 @@
         <v>6</v>
       </c>
       <c r="D5" t="n">
-        <v>7.4966</v>
+        <v>8.6683</v>
       </c>
       <c r="E5" t="n">
-        <v>8.054600000000001</v>
+        <v>8.805400000000001</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.5579000000000001</v>
+        <v>-0.1371999999999999</v>
       </c>
       <c r="G5" t="n">
         <v>-1.9076</v>
@@ -844,13 +844,13 @@
         <v>9.7178</v>
       </c>
       <c r="S5" t="n">
-        <v>-2.2381</v>
+        <v>-1.0664</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.5980999999999999</v>
+        <v>0.1527</v>
       </c>
       <c r="U5" t="n">
-        <v>-1.6401</v>
+        <v>-1.2193</v>
       </c>
       <c r="V5" t="n">
         <v>6.1762</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>L. SOUMBEY-ALLEY</t>
+          <t>N. DEDOVIC</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>6</v>
       </c>
       <c r="D6" t="n">
-        <v>0.4553999999999996</v>
+        <v>3.6993</v>
       </c>
       <c r="E6" t="n">
-        <v>2.3467</v>
+        <v>-0.2582999999999995</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.8914</v>
+        <v>3.9577</v>
       </c>
       <c r="G6" t="n">
-        <v>6.4272</v>
+        <v>-0.8795000000000002</v>
       </c>
       <c r="H6" t="n">
-        <v>-9.4101</v>
+        <v>-2.9981</v>
       </c>
       <c r="I6" t="n">
-        <v>15.8373</v>
+        <v>2.1186</v>
       </c>
       <c r="J6" t="n">
-        <v>10.0362</v>
+        <v>1.5666</v>
       </c>
       <c r="K6" t="n">
-        <v>-4.478</v>
+        <v>0.2529000000000001</v>
       </c>
       <c r="L6" t="n">
-        <v>14.5142</v>
+        <v>1.3139</v>
       </c>
       <c r="M6" t="n">
-        <v>-3.609</v>
+        <v>-2.4462</v>
       </c>
       <c r="N6" t="n">
-        <v>-4.932</v>
+        <v>-3.251</v>
       </c>
       <c r="O6" t="n">
-        <v>1.3232</v>
+        <v>0.8048999999999999</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.8099000000000001</v>
+        <v>4.049</v>
       </c>
       <c r="Q6" t="n">
-        <v>-8.705400000000001</v>
+        <v>-3.8467</v>
       </c>
       <c r="R6" t="n">
-        <v>7.8956</v>
+        <v>7.8957</v>
       </c>
       <c r="S6" t="n">
-        <v>-3.2191</v>
+        <v>0.05370000000000008</v>
       </c>
       <c r="T6" t="n">
-        <v>-1.9595</v>
+        <v>0.3295</v>
       </c>
       <c r="U6" t="n">
-        <v>-1.2594</v>
+        <v>-0.2758</v>
       </c>
       <c r="V6" t="n">
-        <v>-1.943</v>
+        <v>0.476</v>
       </c>
       <c r="W6" t="n">
-        <v>2.9755</v>
+        <v>1.6921</v>
       </c>
       <c r="X6" t="n">
-        <v>-4.9185</v>
+        <v>-1.216</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>N. DEDOVIC</t>
+          <t>L. SOUMBEY-ALLEY</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>6</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.5698999999999997</v>
+        <v>3.4669</v>
       </c>
       <c r="E7" t="n">
-        <v>-3.005999999999999</v>
+        <v>4.758799999999999</v>
       </c>
       <c r="F7" t="n">
-        <v>2.4361</v>
+        <v>-1.2918</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.8795000000000002</v>
+        <v>6.4272</v>
       </c>
       <c r="H7" t="n">
-        <v>-2.9981</v>
+        <v>-9.4101</v>
       </c>
       <c r="I7" t="n">
-        <v>2.1186</v>
+        <v>15.8373</v>
       </c>
       <c r="J7" t="n">
-        <v>1.5666</v>
+        <v>10.0362</v>
       </c>
       <c r="K7" t="n">
-        <v>0.2529000000000001</v>
+        <v>-4.478</v>
       </c>
       <c r="L7" t="n">
-        <v>1.3139</v>
+        <v>14.5142</v>
       </c>
       <c r="M7" t="n">
-        <v>-2.4462</v>
+        <v>-3.609</v>
       </c>
       <c r="N7" t="n">
-        <v>-3.251</v>
+        <v>-4.932</v>
       </c>
       <c r="O7" t="n">
-        <v>0.8048999999999999</v>
+        <v>1.3232</v>
       </c>
       <c r="P7" t="n">
-        <v>4.049</v>
+        <v>-0.8099000000000001</v>
       </c>
       <c r="Q7" t="n">
-        <v>-3.8467</v>
+        <v>-8.705400000000001</v>
       </c>
       <c r="R7" t="n">
-        <v>7.8957</v>
+        <v>7.8956</v>
       </c>
       <c r="S7" t="n">
-        <v>-4.2155</v>
+        <v>-0.2076999999999999</v>
       </c>
       <c r="T7" t="n">
-        <v>-2.4182</v>
+        <v>0.4524</v>
       </c>
       <c r="U7" t="n">
-        <v>-1.7973</v>
+        <v>-0.6597999999999999</v>
       </c>
       <c r="V7" t="n">
-        <v>0.476</v>
+        <v>-1.943</v>
       </c>
       <c r="W7" t="n">
-        <v>1.6921</v>
+        <v>2.9755</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.216</v>
+        <v>-4.9185</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>6</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.9531999999999998</v>
+        <v>2.1506</v>
       </c>
       <c r="E8" t="n">
-        <v>1.9305</v>
+        <v>3.576000000000001</v>
       </c>
       <c r="F8" t="n">
-        <v>-2.8837</v>
+        <v>-1.4255</v>
       </c>
       <c r="G8" t="n">
         <v>-6.7981</v>
@@ -1078,13 +1078,13 @@
         <v>7.8957</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.8791</v>
+        <v>1.2246</v>
       </c>
       <c r="T8" t="n">
-        <v>0.1497000000000002</v>
+        <v>1.7952</v>
       </c>
       <c r="U8" t="n">
-        <v>-2.0287</v>
+        <v>-0.5704</v>
       </c>
       <c r="V8" t="n">
         <v>8.331399999999999</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>L. DIBBA</t>
+          <t>G. CLARKE</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>6</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.3409</v>
+        <v>-2.553</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.6711999999999998</v>
+        <v>-5.0275</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.6698</v>
+        <v>2.4746</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.3996</v>
+        <v>-1.8802</v>
       </c>
       <c r="H9" t="n">
-        <v>0.7332999999999996</v>
+        <v>-8.339700000000001</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.1332</v>
+        <v>6.4595</v>
       </c>
       <c r="J9" t="n">
-        <v>3.1488</v>
+        <v>-1.0928</v>
       </c>
       <c r="K9" t="n">
-        <v>1.8529</v>
+        <v>-5.2636</v>
       </c>
       <c r="L9" t="n">
-        <v>1.2956</v>
+        <v>4.1707</v>
       </c>
       <c r="M9" t="n">
-        <v>-3.5482</v>
+        <v>-0.7875</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.1195</v>
+        <v>-3.0762</v>
       </c>
       <c r="O9" t="n">
-        <v>-2.4287</v>
+        <v>2.2888</v>
       </c>
       <c r="P9" t="n">
-        <v>-2.0246</v>
+        <v>-0.4047999999999999</v>
       </c>
       <c r="Q9" t="n">
-        <v>-7.490899999999999</v>
+        <v>-7.2883</v>
       </c>
       <c r="R9" t="n">
-        <v>5.4663</v>
+        <v>6.8834</v>
       </c>
       <c r="S9" t="n">
-        <v>3.3096</v>
+        <v>-0.8370000000000001</v>
       </c>
       <c r="T9" t="n">
-        <v>2.918</v>
+        <v>-0.4682</v>
       </c>
       <c r="U9" t="n">
-        <v>0.3916</v>
+        <v>-0.3689999999999999</v>
       </c>
       <c r="V9" t="n">
-        <v>-3.2266</v>
+        <v>0.5692999999999996</v>
       </c>
       <c r="W9" t="n">
-        <v>0.7527</v>
+        <v>3.8215</v>
       </c>
       <c r="X9" t="n">
-        <v>-3.9793</v>
+        <v>-3.2522</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>W. CABRAL BUERIBERI</t>
+          <t>R. SANTOS JIMENEZ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1186,76 +1186,76 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.3564</v>
+        <v>-4.3054</v>
       </c>
       <c r="E10" t="n">
-        <v>-7.943000000000001</v>
+        <v>-4.6041</v>
       </c>
       <c r="F10" t="n">
-        <v>4.5867</v>
+        <v>0.2987</v>
       </c>
       <c r="G10" t="n">
-        <v>-3.5031</v>
+        <v>-3.6609</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.3404000000000005</v>
+        <v>-2.4505</v>
       </c>
       <c r="I10" t="n">
-        <v>-3.1628</v>
+        <v>-1.2103</v>
       </c>
       <c r="J10" t="n">
-        <v>1.1382</v>
+        <v>-3.3617</v>
       </c>
       <c r="K10" t="n">
-        <v>2.0813</v>
+        <v>-1.9775</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.9430999999999999</v>
+        <v>-1.3842</v>
       </c>
       <c r="M10" t="n">
-        <v>-4.6412</v>
+        <v>-0.2992</v>
       </c>
       <c r="N10" t="n">
-        <v>-2.4218</v>
+        <v>-0.473</v>
       </c>
       <c r="O10" t="n">
-        <v>-2.2195</v>
+        <v>0.1739</v>
       </c>
       <c r="P10" t="n">
-        <v>-3.4417</v>
+        <v>-0.2024</v>
       </c>
       <c r="Q10" t="n">
-        <v>-11.7423</v>
+        <v>-1.0123</v>
       </c>
       <c r="R10" t="n">
-        <v>8.300599999999999</v>
+        <v>0.8099000000000001</v>
       </c>
       <c r="S10" t="n">
-        <v>3.8036</v>
+        <v>-0.4421</v>
       </c>
       <c r="T10" t="n">
-        <v>1.4347</v>
+        <v>-0.2303</v>
       </c>
       <c r="U10" t="n">
-        <v>2.3687</v>
+        <v>-0.2118</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.2151999999999999</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>1.2259</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.4411</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>G. CLARKE</t>
+          <t>L. DIBBA</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>6</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.502800000000001</v>
+        <v>-5.1646</v>
       </c>
       <c r="E11" t="n">
-        <v>-6.7526</v>
+        <v>-2.9707</v>
       </c>
       <c r="F11" t="n">
-        <v>2.2499</v>
+        <v>-2.194</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.8802</v>
+        <v>-0.3996</v>
       </c>
       <c r="H11" t="n">
-        <v>-8.339700000000001</v>
+        <v>0.7332999999999996</v>
       </c>
       <c r="I11" t="n">
-        <v>6.4595</v>
+        <v>-1.1332</v>
       </c>
       <c r="J11" t="n">
-        <v>-1.0928</v>
+        <v>3.1488</v>
       </c>
       <c r="K11" t="n">
-        <v>-5.2636</v>
+        <v>1.8529</v>
       </c>
       <c r="L11" t="n">
-        <v>4.1707</v>
+        <v>1.2956</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.7875</v>
+        <v>-3.5482</v>
       </c>
       <c r="N11" t="n">
-        <v>-3.0762</v>
+        <v>-1.1195</v>
       </c>
       <c r="O11" t="n">
-        <v>2.2888</v>
+        <v>-2.4287</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.4047999999999999</v>
+        <v>-2.0246</v>
       </c>
       <c r="Q11" t="n">
-        <v>-7.2883</v>
+        <v>-7.490899999999999</v>
       </c>
       <c r="R11" t="n">
-        <v>6.8834</v>
+        <v>5.4663</v>
       </c>
       <c r="S11" t="n">
-        <v>-2.787</v>
+        <v>0.4858999999999999</v>
       </c>
       <c r="T11" t="n">
-        <v>-2.1932</v>
+        <v>0.6185999999999999</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.5939000000000001</v>
+        <v>-0.1327</v>
       </c>
       <c r="V11" t="n">
-        <v>0.5692999999999996</v>
+        <v>-3.2266</v>
       </c>
       <c r="W11" t="n">
-        <v>3.8215</v>
+        <v>0.7527</v>
       </c>
       <c r="X11" t="n">
-        <v>-3.2522</v>
+        <v>-3.9793</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>R. SANTOS JIMENEZ</t>
+          <t>W. CABRAL BUERIBERI</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1342,70 +1342,70 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.6347</v>
+        <v>-5.325899999999999</v>
       </c>
       <c r="E12" t="n">
-        <v>-4.8758</v>
+        <v>-8.789199999999999</v>
       </c>
       <c r="F12" t="n">
-        <v>0.2412</v>
+        <v>3.4631</v>
       </c>
       <c r="G12" t="n">
-        <v>-3.6609</v>
+        <v>-3.5031</v>
       </c>
       <c r="H12" t="n">
-        <v>-2.4505</v>
+        <v>-0.3404000000000005</v>
       </c>
       <c r="I12" t="n">
-        <v>-1.2103</v>
+        <v>-3.1628</v>
       </c>
       <c r="J12" t="n">
-        <v>-3.3617</v>
+        <v>1.1382</v>
       </c>
       <c r="K12" t="n">
-        <v>-1.9775</v>
+        <v>2.0813</v>
       </c>
       <c r="L12" t="n">
-        <v>-1.3842</v>
+        <v>-0.9430999999999999</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.2992</v>
+        <v>-4.6412</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.473</v>
+        <v>-2.4218</v>
       </c>
       <c r="O12" t="n">
-        <v>0.1739</v>
+        <v>-2.2195</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.2024</v>
+        <v>-3.4417</v>
       </c>
       <c r="Q12" t="n">
-        <v>-1.0123</v>
+        <v>-11.7423</v>
       </c>
       <c r="R12" t="n">
-        <v>0.8099000000000001</v>
+        <v>8.300599999999999</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.7714</v>
+        <v>1.8339</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.5019</v>
+        <v>0.5888</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.2695</v>
+        <v>1.2451</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>-0.2151999999999999</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.2259</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>-1.4411</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>6</v>
       </c>
       <c r="D13" t="n">
-        <v>41.2059</v>
+        <v>45.20340000000001</v>
       </c>
       <c r="E13" t="n">
-        <v>27.07520000000001</v>
+        <v>28.9961</v>
       </c>
       <c r="F13" t="n">
-        <v>14.1309</v>
+        <v>16.207</v>
       </c>
       <c r="G13" t="n">
         <v>16.0271</v>
@@ -1438,7 +1438,7 @@
         <v>-21.1527</v>
       </c>
       <c r="I13" t="n">
-        <v>37.1794</v>
+        <v>37.17939999999999</v>
       </c>
       <c r="J13" t="n">
         <v>57.77590000000001</v>
@@ -1453,7 +1453,7 @@
         <v>-41.7486</v>
       </c>
       <c r="N13" t="n">
-        <v>-33.1139</v>
+        <v>-33.11389999999999</v>
       </c>
       <c r="O13" t="n">
         <v>-8.6347</v>
@@ -1462,19 +1462,19 @@
         <v>10.1227</v>
       </c>
       <c r="Q13" t="n">
-        <v>-73.89549999999998</v>
+        <v>-73.8955</v>
       </c>
       <c r="R13" t="n">
         <v>84.0181</v>
       </c>
       <c r="S13" t="n">
-        <v>2.716500000000001</v>
+        <v>6.713899999999999</v>
       </c>
       <c r="T13" t="n">
-        <v>7.602399999999998</v>
+        <v>9.523300000000003</v>
       </c>
       <c r="U13" t="n">
-        <v>-4.885799999999999</v>
+        <v>-2.809</v>
       </c>
       <c r="V13" t="n">
         <v>12.3393</v>
